--- a/metas.xlsx
+++ b/metas.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12312" firstSheet="5" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20892" windowHeight="9180" firstSheet="5" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Estructura de ventas" sheetId="1" r:id="rId1"/>
@@ -5077,7 +5077,7 @@
         <v>165</v>
       </c>
       <c r="B20" s="40" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C20" s="41" t="s">
         <v>168</v>

--- a/metas.xlsx
+++ b/metas.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20892" windowHeight="9180" firstSheet="5" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12312" firstSheet="5" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Estructura de ventas" sheetId="1" r:id="rId1"/>
@@ -4521,7 +4521,7 @@
         <v>105</v>
       </c>
       <c r="B3" s="40" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="C3" s="41" t="s">
         <v>116</v>
